--- a/platform/backend/app/resources/LIS数据标准模板_中文列名.xlsx
+++ b/platform/backend/app/resources/LIS数据标准模板_中文列名.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="字段说明" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="lis_std" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="field_dict" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="field_mapping" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="dict_values" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sample_data" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="quality_rules" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="readme" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lis_std" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="field_dict" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="field_mapping" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dict_values" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sample_data" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quality_rules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="readme" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +53,15 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,8 +83,13 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B5FAA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -99,11 +111,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D5E0ED"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D5E0ED"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D5E0ED"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D5E0ED"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -139,6 +165,16 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,1816 +541,1896 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>列序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>列名(中文)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>英文字段名</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>原始数据来源</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>记录唯一号</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>record_id</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>全局唯一行号</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>系统生成</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>标本条码号</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>barcode</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>跨表连接主键</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>条码号</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>医嘱申请单号</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>开单/申请单标识</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>送检单编码、编号</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>检验单编号</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>test_order_id</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>检验单主键</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>检验单ID</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>项目结果编号</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>result_id</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>单条结果唯一标识</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>项目结果ID</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>样本编号</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>sample_no</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>标本编号</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>样本号、标本编号</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>患者姓名</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>patient_name</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>患者姓名</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>姓名、病人姓名</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>patient_sex</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>枚举</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>男/女/未知</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>性别</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>年龄原文</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>patient_age</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>保留原始文本</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>年龄</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>年龄(岁)</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>patient_age_years</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>折算年数，缺失留空</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>由年龄原文解析</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>病历号</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>patient_id</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>患者主索引</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>病人号、患者ID、His病历号</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>visit_type</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>枚举</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>住院/门诊/急诊</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>类型、就诊类型、病人类别</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>就诊流水号</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>visit_no</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>一次就诊标识</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>就诊流水号</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>申请科室</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>dept_name</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>开单科室</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>科室、申请科室</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>病区名称</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>ward_name</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>病区/护理单元</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>病区、病人病区、报告单元</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>床号</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>bed_no</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>床位号</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>床号、床位号</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>开单医生</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>doctor</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>申请医生</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>医生、申请医生、开立医生</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>临床诊断</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>诊断信息</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>诊断、临床诊断</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>送检目的</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>test_purpose</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>送检类别</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>送检目的、检验目的</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>标本种类</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>specimen_type</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>样本类型</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>标本类型、标本种类、样本类型</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>检验小组</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>test_group</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>专业组别</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>检验分组、检验小组、项目专业</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>检测项目名称</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>test_name</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>项目名称（需别名表）</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>检验项目、医嘱项目</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>项目编码</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>test_code</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>项目唯一编码</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>检验项目编号、医嘱项目编号</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>项目英文名称</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>test_en_name</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>项目英文名</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>英文名称</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>检验仪器</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>instrument</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>上机仪器</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>检验仪器、上机信息、仪器</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>专业</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>test_specialty</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>D标本检测</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>按项目名称对照试剂分类表自动填充</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>试剂分类表·专业</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>组套</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>test_suite</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>D标本检测</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>按项目名称对照试剂分类表自动填充</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>试剂分类表·组套</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>结果数值</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>result_value</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>定量结果，定性留空</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>定量结果、检验结果(可转数)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>结果文本</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>result_text</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>原始结果文本</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>检验结果</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>结果单位</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>计量单位</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>参考范围</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>ref_range</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>参考区间</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>参考范围</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>abnormal_flag</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>枚举</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>偏高/偏低/正常/未知</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>结果状态Code</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>异常箭头</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>abnormal_text</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>↑/↓等符号</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>结果状态</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>申请时间</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>ordered_at</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>开单/申请时刻</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>申请时间、开立时间</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>采集时间</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>collected_at</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>采样时刻</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>采样时间</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>接收时间</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>received_at</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>★标本接收时刻</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>接收时间、核收时间、检验科接收时间</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>上机时间</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="G36" s="4" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>检测开始时刻</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>上机时间、编号时间</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
         <is>
           <t>审核时间</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>verified_at</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>审核时刻</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>审核时间</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
         <is>
           <t>报告时间</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>reported_at</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>★报告发布时刻</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>报告时间、发布时间</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>LIS自带TAT(分钟)</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>tat_minutes</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>厂商算好的分钟数</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>检验中TAT(分钟)、接收-报告(分钟)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>来源实验室</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>source_lab</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>数据来源实验室</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
         <is>
           <t>来源文件</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>原始文件名</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>来源工作表</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>source_sheet</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>原始工作表名</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>表头行号</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>source_header_row</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>表头所在行（从1起）</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>来源行号</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>source_row_number</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>原始数据行号</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
         <is>
           <t>导入批次号</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>import_batch_id</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>批次追踪号</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
@@ -2331,272 +2447,284 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR1"/>
+  <dimension ref="A1:AT1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="25"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="8" customWidth="1" min="31" max="31"/>
-    <col width="8" customWidth="1" min="32" max="32"/>
-    <col width="8" customWidth="1" min="33" max="33"/>
-    <col width="8" customWidth="1" min="34" max="34"/>
-    <col width="8" customWidth="1" min="35" max="35"/>
-    <col width="8" customWidth="1" min="36" max="36"/>
-    <col width="8" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="8" customWidth="1" min="39" max="39"/>
-    <col width="8" customWidth="1" min="40" max="40"/>
-    <col width="8" customWidth="1" min="41" max="41"/>
-    <col width="8" customWidth="1" min="42" max="42"/>
-    <col width="8" customWidth="1" min="43" max="43"/>
-    <col width="8" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="16" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>记录唯一号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>标本条码号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>医嘱申请单号</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>检验单编号</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>项目结果编号</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>样本编号</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>患者姓名</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>年龄原文</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>年龄(岁)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>病历号</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="14" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="14" t="inlineStr">
         <is>
           <t>就诊流水号</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="14" t="inlineStr">
         <is>
           <t>申请科室</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="14" t="inlineStr">
         <is>
           <t>病区名称</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="14" t="inlineStr">
         <is>
           <t>床号</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="14" t="inlineStr">
         <is>
           <t>开单医生</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="14" t="inlineStr">
         <is>
           <t>临床诊断</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="14" t="inlineStr">
         <is>
           <t>送检目的</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="14" t="inlineStr">
         <is>
           <t>标本种类</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="14" t="inlineStr">
         <is>
           <t>检验小组</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="14" t="inlineStr">
         <is>
           <t>检测项目名称</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="14" t="inlineStr">
         <is>
           <t>项目编码</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="14" t="inlineStr">
         <is>
           <t>项目英文名称</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="14" t="inlineStr">
         <is>
           <t>检验仪器</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="14" t="inlineStr">
+        <is>
+          <t>专业</t>
+        </is>
+      </c>
+      <c r="AA1" s="14" t="inlineStr">
+        <is>
+          <t>组套</t>
+        </is>
+      </c>
+      <c r="AB1" s="14" t="inlineStr">
         <is>
           <t>结果数值</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="14" t="inlineStr">
         <is>
           <t>结果文本</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="14" t="inlineStr">
         <is>
           <t>结果单位</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="14" t="inlineStr">
         <is>
           <t>参考范围</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="14" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="14" t="inlineStr">
         <is>
           <t>异常箭头</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="14" t="inlineStr">
         <is>
           <t>申请时间</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="14" t="inlineStr">
         <is>
           <t>采集时间</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="14" t="inlineStr">
         <is>
           <t>接收时间</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="14" t="inlineStr">
         <is>
           <t>上机时间</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="14" t="inlineStr">
         <is>
           <t>审核时间</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="14" t="inlineStr">
         <is>
           <t>报告时间</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="14" t="inlineStr">
         <is>
           <t>LIS自带TAT(分钟)</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="14" t="inlineStr">
         <is>
           <t>来源实验室</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="14" t="inlineStr">
         <is>
           <t>来源文件</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="14" t="inlineStr">
         <is>
           <t>来源工作表</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="14" t="inlineStr">
         <is>
           <t>表头行号</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="14" t="inlineStr">
         <is>
           <t>来源行号</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="14" t="inlineStr">
         <is>
           <t>导入批次号</t>
         </is>
@@ -2613,1678 +2741,1752 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>列名(中文)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>英文字段名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>原始数据来源</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>记录唯一号</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>record_id</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>全局唯一行号</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>系统生成</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>标本条码号</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>barcode</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>跨表连接主键</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>条码号</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>医嘱申请单号</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>开单/申请单标识</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>送检单编码、编号</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>检验单编号</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>test_order_id</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>检验单主键</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>检验单ID</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>项目结果编号</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>result_id</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>单条结果唯一标识</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>项目结果ID</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>样本编号</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>sample_no</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>A标识主键</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>标本编号</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>样本号、标本编号</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>患者姓名</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>patient_name</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>患者姓名</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>姓名、病人姓名</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>patient_sex</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>枚举</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>男/女/未知</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>性别</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>年龄原文</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>patient_age</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>保留原始文本</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>年龄</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>年龄(岁)</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>patient_age_years</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>折算年数，缺失留空</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>由年龄原文解析</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>病历号</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>patient_id</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>患者主索引</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>病人号、患者ID、His病历号</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>visit_type</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>枚举</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>住院/门诊/急诊</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>类型、就诊类型、病人类别</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>就诊流水号</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>visit_no</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>B患者信息</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>一次就诊标识</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>就诊流水号</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>申请科室</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>dept_name</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>开单科室</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>科室、申请科室</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>病区名称</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>ward_name</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>病区/护理单元</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>病区、病人病区、报告单元</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>床号</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>bed_no</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>床位号</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>床号、床位号</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>开单医生</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>doctor</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>申请医生</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>医生、申请医生、开立医生</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>临床诊断</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>diagnosis</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>诊断信息</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>诊断、临床诊断</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>送检目的</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>test_purpose</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>C科室医疗</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>送检类别</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>送检目的、检验目的</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>标本种类</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>specimen_type</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>样本类型</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>标本类型、标本种类、样本类型</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>检验小组</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>test_group</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>专业组别</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>检验分组、检验小组、项目专业</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>检测项目名称</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>test_name</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>项目名称（需别名表）</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>检验项目、医嘱项目</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>项目编码</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>test_code</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>项目唯一编码</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>检验项目编号、医嘱项目编号</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>项目英文名称</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>test_en_name</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>项目英文名</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>英文名称</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>检验仪器</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>instrument</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>D标本检测</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>上机仪器</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>检验仪器、上机信息、仪器</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>专业</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>test_specialty</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D标本检测</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>按项目名称对照试剂分类表自动填充</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>试剂分类表·专业</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>组套</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>test_suite</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>D标本检测</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>按项目名称对照试剂分类表自动填充</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>试剂分类表·组套</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>结果数值</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>result_value</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>定量结果，定性留空</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>定量结果、检验结果(可转数)</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>结果文本</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>result_text</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>原始结果文本</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>检验结果</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>结果单位</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>计量单位</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>参考范围</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>ref_range</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>参考区间</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>参考范围</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>abnormal_flag</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>枚举</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>偏高/偏低/正常/未知</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>结果状态Code</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>异常箭头</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>abnormal_text</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>E结果值</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>↑/↓等符号</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>结果状态</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>申请时间</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>ordered_at</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>开单/申请时刻</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>申请时间、开立时间</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>采集时间</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>collected_at</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>采样时刻</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>采样时间</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>接收时间</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>received_at</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>★标本接收时刻</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>接收时间、核收时间、检验科接收时间</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>上机时间</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>检测开始时刻</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>上机时间、编号时间</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>审核时间</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>verified_at</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>审核时刻</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>审核时间</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>报告时间</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>reported_at</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
         <is>
           <t>日期时间</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>★报告发布时刻</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>报告时间、发布时间</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>LIS自带TAT(分钟)</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>tat_minutes</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>F时间戳</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>厂商算好的分钟数</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>检验中TAT(分钟)、接收-报告(分钟)</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>来源实验室</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>source_lab</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>数据来源实验室</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>来源文件</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>原始文件名</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>来源工作表</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>source_sheet</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>原始工作表名</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>表头行号</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>source_header_row</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>表头所在行（从1起）</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>来源行号</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>source_row_number</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>数值</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>原始数据行号</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>导入批次号</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>import_batch_id</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>G溯源信息</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>文本</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>批次追踪号</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>系统填充</t>
         </is>
@@ -8741,471 +8943,485 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>字段(中文)</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>原始值</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>标准值</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>男性</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>女性</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>未说明</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>住院</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>住院</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>门诊</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>门诊</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>急诊</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>急诊</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>体检</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>体检</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>住院门诊</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>住院</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>门急诊</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>门诊</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>住院</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>OP</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>门诊</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>偏高</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>偏低</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>未知</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>偏高</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>偏低</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>异常箭头</t>
         </is>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>偏高</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>异常箭头</t>
         </is>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>偏低</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>异常箭头</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>偏高</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>异常箭头</t>
         </is>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>偏低</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="C2:C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"偏高,偏低,正常,未知"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"偏高,偏低"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"住院,门诊,急诊,体检"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"男,女,未知"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9216,480 +9432,502 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR2"/>
+  <dimension ref="A1:AT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="8" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="8" customWidth="1" min="23" max="23"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
-    <col width="8" customWidth="1" min="29" max="29"/>
-    <col width="8" customWidth="1" min="30" max="30"/>
-    <col width="8" customWidth="1" min="31" max="31"/>
-    <col width="20" customWidth="1" min="32" max="32"/>
-    <col width="20" customWidth="1" min="33" max="33"/>
-    <col width="20" customWidth="1" min="34" max="34"/>
-    <col width="20" customWidth="1" min="35" max="35"/>
-    <col width="20" customWidth="1" min="36" max="36"/>
-    <col width="20" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="8" customWidth="1" min="39" max="39"/>
-    <col width="20" customWidth="1" min="40" max="40"/>
-    <col width="8" customWidth="1" min="41" max="41"/>
-    <col width="8" customWidth="1" min="42" max="42"/>
-    <col width="8" customWidth="1" min="43" max="43"/>
-    <col width="15" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="16" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="16" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="16" customWidth="1" min="30" max="30"/>
+    <col width="16" customWidth="1" min="31" max="31"/>
+    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
+    <col width="16" customWidth="1" min="35" max="35"/>
+    <col width="16" customWidth="1" min="36" max="36"/>
+    <col width="16" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="40" max="40"/>
+    <col width="16" customWidth="1" min="41" max="41"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="16" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>记录唯一号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>标本条码号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>医嘱申请单号</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>检验单编号</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>项目结果编号</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="14" t="inlineStr">
         <is>
           <t>样本编号</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="14" t="inlineStr">
         <is>
           <t>患者姓名</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="14" t="inlineStr">
         <is>
           <t>患者性别</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="14" t="inlineStr">
         <is>
           <t>年龄原文</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="14" t="inlineStr">
         <is>
           <t>年龄(岁)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="14" t="inlineStr">
         <is>
           <t>病历号</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="14" t="inlineStr">
         <is>
           <t>就诊类型</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="14" t="inlineStr">
         <is>
           <t>就诊流水号</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="14" t="inlineStr">
         <is>
           <t>申请科室</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="14" t="inlineStr">
         <is>
           <t>病区名称</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="14" t="inlineStr">
         <is>
           <t>床号</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="14" t="inlineStr">
         <is>
           <t>开单医生</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="14" t="inlineStr">
         <is>
           <t>临床诊断</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="14" t="inlineStr">
         <is>
           <t>送检目的</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="14" t="inlineStr">
         <is>
           <t>标本种类</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="14" t="inlineStr">
         <is>
           <t>检验小组</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="14" t="inlineStr">
         <is>
           <t>检测项目名称</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="14" t="inlineStr">
         <is>
           <t>项目编码</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="14" t="inlineStr">
         <is>
           <t>项目英文名称</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="14" t="inlineStr">
         <is>
           <t>检验仪器</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="14" t="inlineStr">
+        <is>
+          <t>专业</t>
+        </is>
+      </c>
+      <c r="AA1" s="14" t="inlineStr">
+        <is>
+          <t>组套</t>
+        </is>
+      </c>
+      <c r="AB1" s="14" t="inlineStr">
         <is>
           <t>结果数值</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="14" t="inlineStr">
         <is>
           <t>结果文本</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="14" t="inlineStr">
         <is>
           <t>结果单位</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="14" t="inlineStr">
         <is>
           <t>参考范围</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="14" t="inlineStr">
         <is>
           <t>异常标记</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="14" t="inlineStr">
         <is>
           <t>异常箭头</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="14" t="inlineStr">
         <is>
           <t>申请时间</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="14" t="inlineStr">
         <is>
           <t>采集时间</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="14" t="inlineStr">
         <is>
           <t>接收时间</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="14" t="inlineStr">
         <is>
           <t>上机时间</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="14" t="inlineStr">
         <is>
           <t>审核时间</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="14" t="inlineStr">
         <is>
           <t>报告时间</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="14" t="inlineStr">
         <is>
           <t>LIS自带TAT(分钟)</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="14" t="inlineStr">
         <is>
           <t>来源实验室</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="14" t="inlineStr">
         <is>
           <t>来源文件</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="14" t="inlineStr">
         <is>
           <t>来源工作表</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="14" t="inlineStr">
         <is>
           <t>表头行号</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="14" t="inlineStr">
         <is>
           <t>来源行号</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="14" t="inlineStr">
         <is>
           <t>导入批次号</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>R0000001</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>262601310925</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>SO20260301-0001</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>TO20260301-0001</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>RES0000001</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>305</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="15" t="inlineStr">
         <is>
           <t>鲁忠才</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
+      <c r="I2" s="15" t="inlineStr">
         <is>
           <t>77岁</t>
         </is>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="J2" s="15" t="n">
         <v>77</v>
       </c>
-      <c r="K2" s="10" t="inlineStr">
+      <c r="K2" s="15" t="inlineStr">
         <is>
           <t>2026012824</t>
         </is>
       </c>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="L2" s="15" t="inlineStr">
         <is>
           <t>住院</t>
         </is>
       </c>
-      <c r="M2" s="10" t="inlineStr"/>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="M2" s="15" t="n"/>
+      <c r="N2" s="15" t="inlineStr">
         <is>
           <t>泌尿外科住院</t>
         </is>
       </c>
-      <c r="O2" s="10" t="inlineStr">
+      <c r="O2" s="15" t="inlineStr">
         <is>
           <t>新院区</t>
         </is>
       </c>
-      <c r="P2" s="10" t="inlineStr">
+      <c r="P2" s="15" t="inlineStr">
         <is>
           <t>045</t>
         </is>
       </c>
-      <c r="Q2" s="10" t="inlineStr">
+      <c r="Q2" s="15" t="inlineStr">
         <is>
           <t>贾兴泽</t>
         </is>
       </c>
-      <c r="R2" s="10" t="inlineStr">
+      <c r="R2" s="15" t="inlineStr">
         <is>
           <t>腰痛</t>
         </is>
       </c>
-      <c r="S2" s="10" t="inlineStr">
+      <c r="S2" s="15" t="inlineStr">
         <is>
           <t>常规</t>
         </is>
       </c>
-      <c r="T2" s="10" t="inlineStr">
+      <c r="T2" s="15" t="inlineStr">
         <is>
           <t>血清</t>
         </is>
       </c>
-      <c r="U2" s="10" t="inlineStr">
+      <c r="U2" s="15" t="inlineStr">
         <is>
           <t>迈克MAX生免流水线</t>
         </is>
       </c>
-      <c r="V2" s="10" t="inlineStr">
+      <c r="V2" s="15" t="inlineStr">
         <is>
           <t>白蛋白</t>
         </is>
       </c>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="W2" s="15" t="inlineStr">
         <is>
           <t>10070</t>
         </is>
       </c>
-      <c r="X2" s="10" t="inlineStr">
+      <c r="X2" s="15" t="inlineStr">
         <is>
           <t>ALB</t>
         </is>
       </c>
-      <c r="Y2" s="10" t="inlineStr">
+      <c r="Y2" s="15" t="inlineStr">
         <is>
           <t>LABASMIX_1</t>
         </is>
       </c>
-      <c r="Z2" s="10" t="n">
+      <c r="Z2" s="15" t="inlineStr">
+        <is>
+          <t>生化</t>
+        </is>
+      </c>
+      <c r="AA2" s="15" t="inlineStr">
+        <is>
+          <t>肝功类</t>
+        </is>
+      </c>
+      <c r="AB2" s="15" t="n">
         <v>33.7</v>
       </c>
-      <c r="AA2" s="10" t="inlineStr">
+      <c r="AC2" s="15" t="inlineStr">
         <is>
           <t>33.7</t>
         </is>
       </c>
-      <c r="AB2" s="10" t="inlineStr">
+      <c r="AD2" s="15" t="inlineStr">
         <is>
           <t>g/L</t>
         </is>
       </c>
-      <c r="AC2" s="10" t="inlineStr">
+      <c r="AE2" s="15" t="inlineStr">
         <is>
           <t>35-55</t>
         </is>
       </c>
-      <c r="AD2" s="10" t="inlineStr">
+      <c r="AF2" s="15" t="inlineStr">
         <is>
           <t>偏低</t>
         </is>
       </c>
-      <c r="AE2" s="10" t="inlineStr">
+      <c r="AG2" s="15" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="inlineStr">
+      <c r="AH2" s="15" t="inlineStr">
         <is>
           <t>2026-02-01 07:50:00</t>
         </is>
       </c>
-      <c r="AG2" s="10" t="inlineStr">
+      <c r="AI2" s="15" t="inlineStr">
         <is>
           <t>2026-02-01 07:57:09</t>
         </is>
       </c>
-      <c r="AH2" s="10" t="inlineStr">
+      <c r="AJ2" s="15" t="inlineStr">
         <is>
           <t>2026-02-01 08:34:28</t>
         </is>
       </c>
-      <c r="AI2" s="10" t="inlineStr">
+      <c r="AK2" s="15" t="inlineStr">
         <is>
           <t>2026-02-01 09:10:00</t>
         </is>
       </c>
-      <c r="AJ2" s="10" t="inlineStr">
+      <c r="AL2" s="15" t="inlineStr">
         <is>
           <t>2026-02-01 09:19:27</t>
         </is>
       </c>
-      <c r="AK2" s="10" t="inlineStr">
+      <c r="AM2" s="15" t="inlineStr">
         <is>
           <t>2026-02-01 09:19:27</t>
         </is>
       </c>
-      <c r="AL2" s="10" t="n">
+      <c r="AN2" s="15" t="n">
         <v>45</v>
       </c>
-      <c r="AM2" s="10" t="inlineStr">
+      <c r="AO2" s="15" t="inlineStr">
         <is>
           <t>佳佳</t>
         </is>
       </c>
-      <c r="AN2" s="10" t="inlineStr">
+      <c r="AP2" s="15" t="inlineStr">
         <is>
           <t>样本周转时间查询2026-03-19.xlsx</t>
         </is>
       </c>
-      <c r="AO2" s="10" t="inlineStr">
+      <c r="AQ2" s="15" t="inlineStr">
         <is>
           <t>sheet1</t>
         </is>
       </c>
-      <c r="AP2" s="10" t="n">
+      <c r="AR2" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AQ2" s="10" t="n">
+      <c r="AS2" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="AR2" s="10" t="inlineStr">
+      <c r="AT2" s="15" t="inlineStr">
         <is>
           <t>B20260307-001</t>
         </is>
@@ -9717,232 +9955,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>校验类别</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>规则</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>不通过时处理</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>主键完整性</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>标本条码号 不允许为空</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>拒绝该行</t>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>标本条码号 为空</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>留空并记入提示（不拒绝该行）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>主键完整性</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>检测项目名称 不允许为空</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>拒绝该行</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>检测项目名称 为空</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>留空并记入提示（不拒绝该行）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>时间顺序</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>采集时间 ≤ 接收时间</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>违反记入异常表</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>违反记入提示</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>时间顺序</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>接收时间 ≤ 报告时间</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>违反记入异常表</t>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>违反记入提示</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>时间合理性</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>报告时间 ≥ 采集时间</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>违反记入异常表</t>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>违反记入提示</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>时间合理性</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>LIS自带TAT(分钟) &lt; 0</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>置空，不参与统计</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>时间合理性</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>TAT 列文本如「分钟」「179分钟」</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>正则提取数字，失败置空</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>未来时间</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>任何时间戳不得晚于导入时间+1天</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>拒绝该行</t>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>记入提示</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>日期格式</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>20260701 / 20250401 / 25.09.01</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>统一为 YYYY-MM-DD，缺前缀补 20</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>重复行</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>标本条码号 + 项目编码 不得重复</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>标本条码号 + 项目编码 重复</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>保留最后一条并记录</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>文件格式</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>扩展名与 magic 不符（如 xlsx 实为 xls）</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>按 magic 判断并走对应解析器</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>表头定位</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>表头行号由映射表 header_row 指定</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>不得默认取第 1 行</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>项目分类</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>检测项目名称 / 项目英文名称 对照试剂分类表</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>命中填专业+组套，未命中留空</t>
         </is>
       </c>
     </row>
@@ -9957,257 +10212,286 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="76" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>LIS 数据标准模板 v1.1（中文列名版）</t>
-        </is>
-      </c>
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>LIS 数据标准模板 v1.2（中文列名版 · 取消必填 · 含项目分类）</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="n"/>
-      <c r="B2" s="13" t="n"/>
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>三层结构</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>原始层(只读保留) → 标准层(本模板) → 分析层(TAT/设备负载取子集)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>三层结构</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>原始层(只读保留) → 标准层(本模板) → 分析层(TAT/设备负载取子集)</t>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>列名语言</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>模板表头一律用中文；英文字段名见 field_dict，仅供程序使用</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>列名语言</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>模板表头一律用中文；英文字段名见 field_dict，仅供程序使用</t>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>粒度</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>标准层一行 = 一个检测项目结果</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>粒度</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>标准层一行 = 一个检测项目结果</t>
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>主键</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>标本条码号 是跨表关联的唯一依据</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>主键</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>标本条码号必填，是跨表关联的唯一依据</t>
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>填表原则</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>★ 不设必填：源表有的就填，没有的留空，绝不拒绝整行</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr"/>
-      <c r="B7" s="13" t="inlineStr"/>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>预览规则</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>★ 预览与导出时，某字段在全部数据行都为空则该列不体现</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>项目分类</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>专业 / 组套 两列由检测项目名称、项目英文名称对照试剂分类表自动填充</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>项目名称口径</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>★ 检测项目名称、项目英文名称一律保留原始数据的名称，只新增「专业」「组套」两列，不做任何替换</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>工作表说明</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>字段说明</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>44 列的序号/中文列名/英文字段名/分组/必填/说明/来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>46 列的序号/中文列名/英文字段名/分组/必填/说明/来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>lis_std</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>★标准数据模板，第1行中文列名，勿加标题行，直接填数据</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>field_dict</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>中英对照字典；英文字段名是程序权威 key，勿改</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>field_mapping</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>已实测的映射关系，新增实验室只加行不动表结构</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>dict_values</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>性别/就诊类型/异常标记的枚举对照（标准值也是中文）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>性别/就诊类型枚举对照（标准值也是中文）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>sample_data</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>1 行示例，含偏高标记组合与下拉可选值</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>1 行示例，含项目分类填充效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>quality_rules</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>导入后必须执行的校验规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
-      <c r="B16" s="13" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>导入后执行的校验规则，全部为提示级，不拒绝行</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>时间字段硬规则</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>格式</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>统一 YYYY-MM-DD HH:MM:SS</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>缺失</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>留空，禁止填 0 或当前时间</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>负TAT</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>置空并记入异常表，不参与统计</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
-      <c r="B21" s="13" t="inlineStr"/>
-    </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>实测样本</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>佳佳 2 份 / 孟鹏杰 1 份 / 爱成 3 份，共约 395MB</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>已知坑</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>xlsx 扩展名实为 xls、表头在第 3-4 行、日期三种写法、TAT 列混文本</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
-      <c r="B24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>必填 8 列</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>标本条码号、患者姓名、患者性别、检测项目名称、结果文本、接收时间、报告时间、记录唯一号</t>
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>v1.2 变更</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>取消全部必填；新增专业/组套分类列；预览与导出隐藏全空列</t>
         </is>
       </c>
     </row>
